--- a/artfynd/A 27954-2021 artfynd.xlsx
+++ b/artfynd/A 27954-2021 artfynd.xlsx
@@ -11446,10 +11446,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119540027</v>
+        <v>119539949</v>
       </c>
       <c r="B100" t="n">
-        <v>91310</v>
+        <v>91856</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11458,25 +11458,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1958</v>
+        <v>2059</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -11490,10 +11490,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>540680</v>
+        <v>540590</v>
       </c>
       <c r="R100" t="n">
-        <v>6942953</v>
+        <v>6943641</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11544,7 +11544,7 @@
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>i hålrum under rotben av gammal bränd tallåga</t>
+          <t>sandig mark</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11566,10 +11566,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119540025</v>
+        <v>119539947</v>
       </c>
       <c r="B101" t="n">
-        <v>80483</v>
+        <v>91884</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11582,21 +11582,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1049</v>
+        <v>5449</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -11610,10 +11610,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540645</v>
+        <v>540559</v>
       </c>
       <c r="R101" t="n">
-        <v>6942999</v>
+        <v>6943714</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>grov gammal skorstenshögstubbe</t>
+          <t>sandig mark</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11686,10 +11686,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119539955</v>
+        <v>119540027</v>
       </c>
       <c r="B102" t="n">
-        <v>91834</v>
+        <v>91310</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11698,25 +11698,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -11730,10 +11730,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540583</v>
+        <v>540680</v>
       </c>
       <c r="R102" t="n">
-        <v>6943542</v>
+        <v>6942953</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -11806,10 +11806,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119539949</v>
+        <v>119540025</v>
       </c>
       <c r="B103" t="n">
-        <v>91856</v>
+        <v>80483</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11822,21 +11822,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2059</v>
+        <v>1049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -11850,10 +11850,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540590</v>
+        <v>540645</v>
       </c>
       <c r="R103" t="n">
-        <v>6943641</v>
+        <v>6942999</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11904,7 +11904,7 @@
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>sandig mark</t>
+          <t>grov gammal skorstenshögstubbe</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -11926,10 +11926,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119539947</v>
+        <v>119539955</v>
       </c>
       <c r="B104" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11942,21 +11942,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -11970,10 +11970,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>540559</v>
+        <v>540583</v>
       </c>
       <c r="R104" t="n">
-        <v>6943714</v>
+        <v>6943542</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12019,12 +12019,12 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>sandig mark</t>
+          <t>i hålrum under rotben av gammal bränd tallåga</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -12046,10 +12046,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119539962</v>
+        <v>119539988</v>
       </c>
       <c r="B105" t="n">
-        <v>90712</v>
+        <v>78263</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12058,25 +12058,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -12090,10 +12090,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540625</v>
+        <v>540570</v>
       </c>
       <c r="R105" t="n">
-        <v>6943399</v>
+        <v>6943318</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12139,12 +12139,12 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>140-årig, lövrik tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>grov rest av gammal tallåga med brandspår</t>
+          <t>mycket grov, 4 m hög tallhögsubbe, med kol ända upp</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12166,10 +12166,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119540022</v>
+        <v>119539962</v>
       </c>
       <c r="B106" t="n">
-        <v>90399</v>
+        <v>90712</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12178,25 +12178,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6020</v>
+        <v>1503</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -12210,10 +12210,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540595</v>
+        <v>540625</v>
       </c>
       <c r="R106" t="n">
-        <v>6943080</v>
+        <v>6943399</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12259,12 +12259,12 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog med lövinslag på blockig frisk moränmark</t>
+          <t>140-årig, lövrik tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>på bark under hängande, ca 10 år gammal asplåga av 130-årig asp, 22 cm bred</t>
+          <t>grov rest av gammal tallåga med brandspår</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12286,10 +12286,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119539976</v>
+        <v>119540022</v>
       </c>
       <c r="B107" t="n">
-        <v>79607</v>
+        <v>90399</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12302,26 +12302,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>6020</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12330,10 +12330,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540597</v>
+        <v>540595</v>
       </c>
       <c r="R107" t="n">
-        <v>6943485</v>
+        <v>6943080</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12379,7 +12379,12 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
+          <t>140-årig tallnaturskog med lövinslag på blockig frisk moränmark</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>på bark under hängande, ca 10 år gammal asplåga av 130-årig asp, 22 cm bred</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12401,10 +12406,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119539988</v>
+        <v>119539976</v>
       </c>
       <c r="B108" t="n">
-        <v>78263</v>
+        <v>79607</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12417,26 +12422,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -12445,10 +12450,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>540570</v>
+        <v>540597</v>
       </c>
       <c r="R108" t="n">
-        <v>6943318</v>
+        <v>6943485</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12494,12 +12499,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>mycket grov, 4 m hög tallhögsubbe, med kol ända upp</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12881,10 +12881,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119539952</v>
+        <v>119539945</v>
       </c>
       <c r="B112" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12897,21 +12897,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -12925,10 +12925,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>540543</v>
+        <v>540496</v>
       </c>
       <c r="R112" t="n">
-        <v>6943622</v>
+        <v>6943786</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12979,7 +12979,7 @@
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>fallen brandstubbe</t>
+          <t>mycket grov och hög gammal brandhögstubbe</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -13001,10 +13001,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119539953</v>
+        <v>119539972</v>
       </c>
       <c r="B113" t="n">
-        <v>89252</v>
+        <v>78263</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13013,30 +13013,30 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13045,10 +13045,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540526</v>
+        <v>540533</v>
       </c>
       <c r="R113" t="n">
-        <v>6943618</v>
+        <v>6943520</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13094,12 +13094,12 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>sandig fläck</t>
+          <t>grova gamla branhögstubbar, delvis av skostenstyp</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -13121,10 +13121,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119540015</v>
+        <v>119540017</v>
       </c>
       <c r="B114" t="n">
-        <v>79144</v>
+        <v>79115</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13137,21 +13137,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -13165,10 +13165,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540603</v>
+        <v>540587</v>
       </c>
       <c r="R114" t="n">
-        <v>6943140</v>
+        <v>6943110</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13219,7 +13219,7 @@
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>bränd gammal rest av tallåga</t>
+          <t>grov och hård gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -13241,10 +13241,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119539945</v>
+        <v>119539952</v>
       </c>
       <c r="B115" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13257,21 +13257,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -13285,10 +13285,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540496</v>
+        <v>540543</v>
       </c>
       <c r="R115" t="n">
-        <v>6943786</v>
+        <v>6943622</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>mycket grov och hög gammal brandhögstubbe</t>
+          <t>fallen brandstubbe</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -13361,10 +13361,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119539972</v>
+        <v>119539953</v>
       </c>
       <c r="B116" t="n">
-        <v>78263</v>
+        <v>89252</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13373,30 +13373,30 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13405,10 +13405,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540533</v>
+        <v>540526</v>
       </c>
       <c r="R116" t="n">
-        <v>6943520</v>
+        <v>6943618</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13454,12 +13454,12 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>grova gamla branhögstubbar, delvis av skostenstyp</t>
+          <t>sandig fläck</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -13481,10 +13481,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119540017</v>
+        <v>119540015</v>
       </c>
       <c r="B117" t="n">
-        <v>79115</v>
+        <v>79144</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13497,21 +13497,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -13525,10 +13525,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540587</v>
+        <v>540603</v>
       </c>
       <c r="R117" t="n">
-        <v>6943110</v>
+        <v>6943140</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13579,7 +13579,7 @@
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>grov och hård gammal tallhögstubbe</t>
+          <t>bränd gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -13601,10 +13601,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119539964</v>
+        <v>119539960</v>
       </c>
       <c r="B118" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13613,42 +13613,38 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540615</v>
+        <v>540627</v>
       </c>
       <c r="R118" t="n">
-        <v>6943357</v>
+        <v>6943420</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13694,12 +13690,7 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>asphögstubbe av senvuxen gammal asp</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13721,10 +13712,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119539960</v>
+        <v>119539964</v>
       </c>
       <c r="B119" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13733,38 +13724,42 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540627</v>
+        <v>540615</v>
       </c>
       <c r="R119" t="n">
-        <v>6943420</v>
+        <v>6943357</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13810,7 +13805,12 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>asphögstubbe av senvuxen gammal asp</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -14432,10 +14432,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119539943</v>
+        <v>119539950</v>
       </c>
       <c r="B125" t="n">
-        <v>79144</v>
+        <v>92030</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14448,34 +14448,38 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540529</v>
+        <v>540558</v>
       </c>
       <c r="R125" t="n">
-        <v>6943889</v>
+        <v>6943647</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14526,7 +14530,7 @@
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>grova gamla tallstubbar från dimensionsavverkningen</t>
+          <t>bränd gammal tallåga</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -14548,10 +14552,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119539940</v>
+        <v>119539943</v>
       </c>
       <c r="B126" t="n">
-        <v>91884</v>
+        <v>79144</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14564,21 +14568,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14588,10 +14592,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>540551</v>
+        <v>540529</v>
       </c>
       <c r="R126" t="n">
-        <v>6943379</v>
+        <v>6943889</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14637,12 +14641,12 @@
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr sandig moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>sandfläck</t>
+          <t>grova gamla tallstubbar från dimensionsavverkningen</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -14664,10 +14668,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119539950</v>
+        <v>119539940</v>
       </c>
       <c r="B127" t="n">
-        <v>92030</v>
+        <v>91884</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14680,38 +14684,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2079</v>
+        <v>5449</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>540558</v>
+        <v>540551</v>
       </c>
       <c r="R127" t="n">
-        <v>6943647</v>
+        <v>6943379</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14757,12 +14757,12 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr sandig moränmark</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>bränd gammal tallåga</t>
+          <t>sandfläck</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>

--- a/artfynd/A 27954-2021 artfynd.xlsx
+++ b/artfynd/A 27954-2021 artfynd.xlsx
@@ -9442,10 +9442,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119540018</v>
+        <v>119539948</v>
       </c>
       <c r="B83" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9458,26 +9458,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9486,10 +9486,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540587</v>
+        <v>540596</v>
       </c>
       <c r="R83" t="n">
-        <v>6943110</v>
+        <v>6943630</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9540,7 +9540,7 @@
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>grov och hård gammal tallhögstubbe</t>
+          <t>gamla hårda tallågor</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9562,7 +9562,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119539948</v>
+        <v>119540007</v>
       </c>
       <c r="B84" t="n">
         <v>78171</v>
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540596</v>
+        <v>540649</v>
       </c>
       <c r="R84" t="n">
-        <v>6943630</v>
+        <v>6943183</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>gamla hårda tallågor</t>
+          <t>gamla klena men hårda tallågor, hängande på block</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9682,10 +9682,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119540007</v>
+        <v>119539989</v>
       </c>
       <c r="B85" t="n">
-        <v>78171</v>
+        <v>80483</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9698,26 +9698,26 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>1049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9726,10 +9726,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540649</v>
+        <v>540566</v>
       </c>
       <c r="R85" t="n">
-        <v>6943183</v>
+        <v>6943314</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9775,12 +9775,12 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>gamla klena men hårda tallågor, hängande på block</t>
+          <t>mycket grov skorstenshögsubbe, ser ut att ha varit boplats för slaguggla</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9802,10 +9802,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119539989</v>
+        <v>119540018</v>
       </c>
       <c r="B86" t="n">
-        <v>80483</v>
+        <v>78262</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9818,21 +9818,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9846,10 +9846,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540566</v>
+        <v>540587</v>
       </c>
       <c r="R86" t="n">
-        <v>6943314</v>
+        <v>6943110</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9895,12 +9895,12 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>mycket grov skorstenshögsubbe, ser ut att ha varit boplats för slaguggla</t>
+          <t>grov och hård gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -12046,10 +12046,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119539988</v>
+        <v>119539962</v>
       </c>
       <c r="B105" t="n">
-        <v>78263</v>
+        <v>90712</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12058,25 +12058,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -12090,10 +12090,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540570</v>
+        <v>540625</v>
       </c>
       <c r="R105" t="n">
-        <v>6943318</v>
+        <v>6943399</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12139,12 +12139,12 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig, lövrik tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>mycket grov, 4 m hög tallhögsubbe, med kol ända upp</t>
+          <t>grov rest av gammal tallåga med brandspår</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12166,10 +12166,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119539962</v>
+        <v>119540022</v>
       </c>
       <c r="B106" t="n">
-        <v>90712</v>
+        <v>90399</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12178,25 +12178,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1503</v>
+        <v>6020</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -12210,10 +12210,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540625</v>
+        <v>540595</v>
       </c>
       <c r="R106" t="n">
-        <v>6943399</v>
+        <v>6943080</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12259,12 +12259,12 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>140-årig, lövrik tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog med lövinslag på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>grov rest av gammal tallåga med brandspår</t>
+          <t>på bark under hängande, ca 10 år gammal asplåga av 130-årig asp, 22 cm bred</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12286,10 +12286,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119540022</v>
+        <v>119539976</v>
       </c>
       <c r="B107" t="n">
-        <v>90399</v>
+        <v>79607</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12302,26 +12302,26 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6020</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12330,10 +12330,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540595</v>
+        <v>540597</v>
       </c>
       <c r="R107" t="n">
-        <v>6943080</v>
+        <v>6943485</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12379,12 +12379,7 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog med lövinslag på blockig frisk moränmark</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>på bark under hängande, ca 10 år gammal asplåga av 130-årig asp, 22 cm bred</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12406,10 +12401,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119539976</v>
+        <v>119539988</v>
       </c>
       <c r="B108" t="n">
-        <v>79607</v>
+        <v>78263</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12422,26 +12417,26 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -12450,10 +12445,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>540597</v>
+        <v>540570</v>
       </c>
       <c r="R108" t="n">
-        <v>6943485</v>
+        <v>6943318</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12499,7 +12494,12 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>mycket grov, 4 m hög tallhögsubbe, med kol ända upp</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12881,10 +12881,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119539945</v>
+        <v>119539952</v>
       </c>
       <c r="B112" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12897,21 +12897,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -12925,10 +12925,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>540496</v>
+        <v>540543</v>
       </c>
       <c r="R112" t="n">
-        <v>6943786</v>
+        <v>6943622</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12979,7 +12979,7 @@
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>mycket grov och hög gammal brandhögstubbe</t>
+          <t>fallen brandstubbe</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -13001,10 +13001,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119539972</v>
+        <v>119539953</v>
       </c>
       <c r="B113" t="n">
-        <v>78263</v>
+        <v>89252</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13013,30 +13013,30 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13045,10 +13045,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540533</v>
+        <v>540526</v>
       </c>
       <c r="R113" t="n">
-        <v>6943520</v>
+        <v>6943618</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13094,12 +13094,12 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>grova gamla branhögstubbar, delvis av skostenstyp</t>
+          <t>sandig fläck</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -13121,10 +13121,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119540017</v>
+        <v>119540015</v>
       </c>
       <c r="B114" t="n">
-        <v>79115</v>
+        <v>79144</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13137,21 +13137,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -13165,10 +13165,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540587</v>
+        <v>540603</v>
       </c>
       <c r="R114" t="n">
-        <v>6943110</v>
+        <v>6943140</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13219,7 +13219,7 @@
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>grov och hård gammal tallhögstubbe</t>
+          <t>bränd gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -13241,10 +13241,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119539952</v>
+        <v>119539945</v>
       </c>
       <c r="B115" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13257,21 +13257,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -13285,10 +13285,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540543</v>
+        <v>540496</v>
       </c>
       <c r="R115" t="n">
-        <v>6943622</v>
+        <v>6943786</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13339,7 +13339,7 @@
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>fallen brandstubbe</t>
+          <t>mycket grov och hög gammal brandhögstubbe</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -13361,10 +13361,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119539953</v>
+        <v>119539972</v>
       </c>
       <c r="B116" t="n">
-        <v>89252</v>
+        <v>78263</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13373,30 +13373,30 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13405,10 +13405,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540526</v>
+        <v>540533</v>
       </c>
       <c r="R116" t="n">
-        <v>6943618</v>
+        <v>6943520</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13454,12 +13454,12 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>sandig fläck</t>
+          <t>grova gamla branhögstubbar, delvis av skostenstyp</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -13481,10 +13481,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119540015</v>
+        <v>119540017</v>
       </c>
       <c r="B117" t="n">
-        <v>79144</v>
+        <v>79115</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13497,21 +13497,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -13525,10 +13525,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540603</v>
+        <v>540587</v>
       </c>
       <c r="R117" t="n">
-        <v>6943140</v>
+        <v>6943110</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13579,7 +13579,7 @@
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>bränd gammal rest av tallåga</t>
+          <t>grov och hård gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -13601,10 +13601,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119539960</v>
+        <v>119539964</v>
       </c>
       <c r="B118" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13613,38 +13613,42 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540627</v>
+        <v>540615</v>
       </c>
       <c r="R118" t="n">
-        <v>6943420</v>
+        <v>6943357</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13690,7 +13694,12 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>asphögstubbe av senvuxen gammal asp</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13712,10 +13721,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119539964</v>
+        <v>119539960</v>
       </c>
       <c r="B119" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13724,42 +13733,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540615</v>
+        <v>540627</v>
       </c>
       <c r="R119" t="n">
-        <v>6943357</v>
+        <v>6943420</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13805,12 +13810,7 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>asphögstubbe av senvuxen gammal asp</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>

--- a/artfynd/A 27954-2021 artfynd.xlsx
+++ b/artfynd/A 27954-2021 artfynd.xlsx
@@ -9322,10 +9322,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119540024</v>
+        <v>119540028</v>
       </c>
       <c r="B82" t="n">
-        <v>90712</v>
+        <v>78263</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9334,25 +9334,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -9366,10 +9366,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540648</v>
+        <v>540675</v>
       </c>
       <c r="R82" t="n">
-        <v>6943001</v>
+        <v>6942950</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9420,7 +9420,7 @@
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>sidan av gammal tallåga med mosshätta</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9442,10 +9442,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119539948</v>
+        <v>119539955</v>
       </c>
       <c r="B83" t="n">
-        <v>78171</v>
+        <v>91834</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9458,26 +9458,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9486,10 +9486,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540596</v>
+        <v>540583</v>
       </c>
       <c r="R83" t="n">
-        <v>6943630</v>
+        <v>6943542</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9535,12 +9535,12 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>gamla hårda tallågor</t>
+          <t>i hålrum under rotben av gammal bränd tallåga</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9562,10 +9562,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119540007</v>
+        <v>119539999</v>
       </c>
       <c r="B84" t="n">
-        <v>78171</v>
+        <v>90576</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9578,26 +9578,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>1204</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9606,10 +9606,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540649</v>
+        <v>540637</v>
       </c>
       <c r="R84" t="n">
-        <v>6943183</v>
+        <v>6943297</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9655,12 +9655,12 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>gamla klena men hårda tallågor, hängande på block</t>
+          <t>grov gammal tallåga</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9682,7 +9682,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119539989</v>
+        <v>119540025</v>
       </c>
       <c r="B85" t="n">
         <v>80483</v>
@@ -9726,10 +9726,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540566</v>
+        <v>540645</v>
       </c>
       <c r="R85" t="n">
-        <v>6943314</v>
+        <v>6942999</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9775,12 +9775,12 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>mycket grov skorstenshögsubbe, ser ut att ha varit boplats för slaguggla</t>
+          <t>grov gammal skorstenshögstubbe</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9802,10 +9802,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119540018</v>
+        <v>119539964</v>
       </c>
       <c r="B86" t="n">
-        <v>78262</v>
+        <v>79607</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9818,21 +9818,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -9846,10 +9846,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540587</v>
+        <v>540615</v>
       </c>
       <c r="R86" t="n">
-        <v>6943110</v>
+        <v>6943357</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9895,12 +9895,12 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>grov och hård gammal tallhögstubbe</t>
+          <t>asphögstubbe av senvuxen gammal asp</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -9922,10 +9922,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119539973</v>
+        <v>119539948</v>
       </c>
       <c r="B87" t="n">
-        <v>90058</v>
+        <v>78171</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9938,34 +9938,38 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5734</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Druvfingersvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramaria botrytis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bourdot</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540583</v>
+        <v>540596</v>
       </c>
       <c r="R87" t="n">
-        <v>6943506</v>
+        <v>6943630</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10011,7 +10015,12 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>gamla hårda tallågor</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10033,10 +10042,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119539941</v>
+        <v>119539946</v>
       </c>
       <c r="B88" t="n">
-        <v>91884</v>
+        <v>78171</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10049,34 +10058,38 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540526</v>
+        <v>540509</v>
       </c>
       <c r="R88" t="n">
-        <v>6943625</v>
+        <v>6943761</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10122,7 +10135,12 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr sandig moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>gammal vindfälld tallåga</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10144,10 +10162,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119539999</v>
+        <v>119540018</v>
       </c>
       <c r="B89" t="n">
-        <v>90576</v>
+        <v>78262</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10160,21 +10178,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1204</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -10188,10 +10206,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540637</v>
+        <v>540587</v>
       </c>
       <c r="R89" t="n">
-        <v>6943297</v>
+        <v>6943110</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10237,12 +10255,12 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>grov gammal tallåga</t>
+          <t>grov och hård gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10264,10 +10282,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119540023</v>
+        <v>119540013</v>
       </c>
       <c r="B90" t="n">
-        <v>79567</v>
+        <v>89633</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10276,30 +10294,30 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229497</v>
+        <v>1962</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10308,10 +10326,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540680</v>
+        <v>540603</v>
       </c>
       <c r="R90" t="n">
-        <v>6942997</v>
+        <v>6943140</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10357,12 +10375,12 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog med lövinslag på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>grova gamla aspar</t>
+          <t>under bränd gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10384,10 +10402,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119539975</v>
+        <v>119539965</v>
       </c>
       <c r="B91" t="n">
-        <v>87406</v>
+        <v>91856</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10400,34 +10418,38 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4412</v>
+        <v>2059</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540583</v>
+        <v>540562</v>
       </c>
       <c r="R91" t="n">
-        <v>6943504</v>
+        <v>6943482</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10473,7 +10495,12 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>sandig fläck</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10495,10 +10522,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119539967</v>
+        <v>119539943</v>
       </c>
       <c r="B92" t="n">
-        <v>89964</v>
+        <v>79144</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10507,42 +10534,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5685</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>540570</v>
+        <v>540529</v>
       </c>
       <c r="R92" t="n">
-        <v>6943440</v>
+        <v>6943889</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10588,12 +10611,12 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>äldre murket tallvindfälle</t>
+          <t>grova gamla tallstubbar från dimensionsavverkningen</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10615,10 +10638,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119539957</v>
+        <v>119539940</v>
       </c>
       <c r="B93" t="n">
-        <v>91547</v>
+        <v>91884</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10627,25 +10650,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5836</v>
+        <v>5449</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10655,10 +10678,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540602</v>
+        <v>540551</v>
       </c>
       <c r="R93" t="n">
-        <v>6943483</v>
+        <v>6943379</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10704,7 +10727,12 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
+          <t>140-årig tallnaturskog på blockig torr sandig moränmark</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>sandfläck</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10726,10 +10754,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119540009</v>
+        <v>119539949</v>
       </c>
       <c r="B94" t="n">
-        <v>78263</v>
+        <v>91856</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10742,21 +10770,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -10770,10 +10798,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>540648</v>
+        <v>540590</v>
       </c>
       <c r="R94" t="n">
-        <v>6943157</v>
+        <v>6943641</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10824,7 +10852,7 @@
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>7 m hög, grov gammal tallhögstubbe med brandspår</t>
+          <t>sandig mark</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -10846,10 +10874,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119539994</v>
+        <v>119540026</v>
       </c>
       <c r="B95" t="n">
-        <v>90712</v>
+        <v>78171</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10858,25 +10886,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -10890,10 +10918,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540593</v>
+        <v>540609</v>
       </c>
       <c r="R95" t="n">
-        <v>6943335</v>
+        <v>6942963</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10939,12 +10967,12 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
-          <t>gammal, grov tallåga, upphängd mot block</t>
+          <t>grov äldre tallåga</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -10966,10 +10994,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119540004</v>
+        <v>119539941</v>
       </c>
       <c r="B96" t="n">
-        <v>91886</v>
+        <v>91884</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10978,42 +11006,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>232140</v>
+        <v>5449</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540626</v>
+        <v>540526</v>
       </c>
       <c r="R96" t="n">
-        <v>6943267</v>
+        <v>6943625</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11059,12 +11083,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>sandig mark under äldre, klen, självgallrad tallåga</t>
+          <t>140-årig tallnaturskog på blockig torr sandig moränmark</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11086,10 +11105,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119539970</v>
+        <v>119539959</v>
       </c>
       <c r="B97" t="n">
-        <v>78171</v>
+        <v>86410</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11098,42 +11117,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>353</v>
+        <v>249228</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540558</v>
+        <v>540617</v>
       </c>
       <c r="R97" t="n">
-        <v>6943477</v>
+        <v>6943447</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11179,12 +11194,12 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>grov rest av gammal tallåga med brandspår</t>
+          <t>barrmatta under grov gran</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11206,10 +11221,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119539979</v>
+        <v>119539950</v>
       </c>
       <c r="B98" t="n">
-        <v>90573</v>
+        <v>92030</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11218,25 +11233,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1205</v>
+        <v>2079</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -11250,10 +11265,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>540597</v>
+        <v>540558</v>
       </c>
       <c r="R98" t="n">
-        <v>6943485</v>
+        <v>6943647</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11299,12 +11314,12 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>grövre asplåga</t>
+          <t>bränd gammal tallåga</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11326,10 +11341,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119539944</v>
+        <v>119539962</v>
       </c>
       <c r="B99" t="n">
-        <v>79115</v>
+        <v>90712</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11338,25 +11353,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -11370,10 +11385,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>540529</v>
+        <v>540625</v>
       </c>
       <c r="R99" t="n">
-        <v>6943889</v>
+        <v>6943399</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11419,12 +11434,12 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig, lövrik tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>grov gammal tallstubbe från dimensionsavverkningen</t>
+          <t>grov rest av gammal tallåga med brandspår</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11446,10 +11461,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119539949</v>
+        <v>119539947</v>
       </c>
       <c r="B100" t="n">
-        <v>91856</v>
+        <v>91884</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11462,21 +11477,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -11490,10 +11505,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>540590</v>
+        <v>540559</v>
       </c>
       <c r="R100" t="n">
-        <v>6943641</v>
+        <v>6943714</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11566,10 +11581,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119539947</v>
+        <v>119540020</v>
       </c>
       <c r="B101" t="n">
-        <v>91884</v>
+        <v>78263</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11582,26 +11597,26 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -11610,10 +11625,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540559</v>
+        <v>540601</v>
       </c>
       <c r="R101" t="n">
-        <v>6943714</v>
+        <v>6943111</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11664,7 +11679,7 @@
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>sandig mark</t>
+          <t>grova gamla brandstubbar</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11686,10 +11701,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119540027</v>
+        <v>119540004</v>
       </c>
       <c r="B102" t="n">
-        <v>91310</v>
+        <v>91886</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11702,21 +11717,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1958</v>
+        <v>232140</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -11730,10 +11745,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540680</v>
+        <v>540626</v>
       </c>
       <c r="R102" t="n">
-        <v>6942953</v>
+        <v>6943267</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11779,12 +11794,12 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>i hålrum under rotben av gammal bränd tallåga</t>
+          <t>sandig mark under äldre, klen, självgallrad tallåga</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -11806,10 +11821,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119540025</v>
+        <v>119539996</v>
       </c>
       <c r="B103" t="n">
-        <v>80483</v>
+        <v>92030</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11822,21 +11837,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1049</v>
+        <v>2079</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -11850,10 +11865,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540645</v>
+        <v>540597</v>
       </c>
       <c r="R103" t="n">
-        <v>6942999</v>
+        <v>6943340</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11899,12 +11914,12 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>grov gammal skorstenshögstubbe</t>
+          <t>gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -11926,10 +11941,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119539955</v>
+        <v>119539970</v>
       </c>
       <c r="B104" t="n">
-        <v>91834</v>
+        <v>78171</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11942,21 +11957,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4362</v>
+        <v>353</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -11970,10 +11985,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>540583</v>
+        <v>540558</v>
       </c>
       <c r="R104" t="n">
-        <v>6943542</v>
+        <v>6943477</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12019,12 +12034,12 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>i hålrum under rotben av gammal bränd tallåga</t>
+          <t>grov rest av gammal tallåga med brandspår</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -12046,10 +12061,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119539962</v>
+        <v>119540012</v>
       </c>
       <c r="B105" t="n">
-        <v>90712</v>
+        <v>78171</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12058,30 +12073,30 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -12090,10 +12105,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540625</v>
+        <v>540638</v>
       </c>
       <c r="R105" t="n">
-        <v>6943399</v>
+        <v>6943153</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12139,12 +12154,12 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>140-årig, lövrik tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>grov rest av gammal tallåga med brandspår</t>
+          <t>gamla klena men hårda tallågor, hängande på block</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12166,10 +12181,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119540022</v>
+        <v>119540002</v>
       </c>
       <c r="B106" t="n">
-        <v>90399</v>
+        <v>91883</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12182,21 +12197,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6020</v>
+        <v>5448</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -12210,10 +12225,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540595</v>
+        <v>540623</v>
       </c>
       <c r="R106" t="n">
-        <v>6943080</v>
+        <v>6943285</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12259,12 +12274,12 @@
       </c>
       <c r="AI106" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog med lövinslag på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>på bark under hängande, ca 10 år gammal asplåga av 130-årig asp, 22 cm bred</t>
+          <t>sandig mark under gammal murken tallåga</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12286,10 +12301,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119539976</v>
+        <v>119539994</v>
       </c>
       <c r="B107" t="n">
-        <v>79607</v>
+        <v>90712</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12298,30 +12313,30 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6458</v>
+        <v>1503</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12330,10 +12345,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540597</v>
+        <v>540593</v>
       </c>
       <c r="R107" t="n">
-        <v>6943485</v>
+        <v>6943335</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12379,7 +12394,12 @@
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>gammal, grov tallåga, upphängd mot block</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12401,10 +12421,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119539988</v>
+        <v>119539960</v>
       </c>
       <c r="B108" t="n">
-        <v>78263</v>
+        <v>97907</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12413,42 +12433,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>540570</v>
+        <v>540627</v>
       </c>
       <c r="R108" t="n">
-        <v>6943318</v>
+        <v>6943420</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12494,12 +12510,7 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>mycket grov, 4 m hög tallhögsubbe, med kol ända upp</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12521,10 +12532,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119539965</v>
+        <v>119539945</v>
       </c>
       <c r="B109" t="n">
-        <v>91856</v>
+        <v>78263</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12537,21 +12548,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -12565,10 +12576,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>540562</v>
+        <v>540496</v>
       </c>
       <c r="R109" t="n">
-        <v>6943482</v>
+        <v>6943786</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12614,12 +12625,12 @@
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>sandig fläck</t>
+          <t>mycket grov och hög gammal brandhögstubbe</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12641,10 +12652,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119540021</v>
+        <v>119539954</v>
       </c>
       <c r="B110" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12657,21 +12668,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -12685,10 +12696,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>540594</v>
+        <v>540579</v>
       </c>
       <c r="R110" t="n">
-        <v>6943086</v>
+        <v>6943545</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12739,7 +12750,7 @@
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>äldre tallåga, vindfälle</t>
+          <t>grova gammal brandhögstubbe</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12761,10 +12772,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119540012</v>
+        <v>119539967</v>
       </c>
       <c r="B111" t="n">
-        <v>78171</v>
+        <v>89964</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12773,30 +12784,30 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>353</v>
+        <v>5685</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -12805,10 +12816,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>540638</v>
+        <v>540570</v>
       </c>
       <c r="R111" t="n">
-        <v>6943153</v>
+        <v>6943440</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12854,12 +12865,12 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>gamla klena men hårda tallågor, hängande på block</t>
+          <t>äldre murket tallvindfälle</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -12881,10 +12892,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119539952</v>
+        <v>119539944</v>
       </c>
       <c r="B112" t="n">
-        <v>78171</v>
+        <v>79115</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12897,21 +12908,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -12925,10 +12936,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>540543</v>
+        <v>540529</v>
       </c>
       <c r="R112" t="n">
-        <v>6943622</v>
+        <v>6943889</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12979,7 +12990,7 @@
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>fallen brandstubbe</t>
+          <t>grov gammal tallstubbe från dimensionsavverkningen</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -13001,10 +13012,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119539953</v>
+        <v>119540007</v>
       </c>
       <c r="B113" t="n">
-        <v>89252</v>
+        <v>78171</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13013,30 +13024,30 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6276</v>
+        <v>353</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13045,10 +13056,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540526</v>
+        <v>540649</v>
       </c>
       <c r="R113" t="n">
-        <v>6943618</v>
+        <v>6943183</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13094,12 +13105,12 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>sandig fläck</t>
+          <t>gamla klena men hårda tallågor, hängande på block</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -13121,10 +13132,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119540015</v>
+        <v>119539972</v>
       </c>
       <c r="B114" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13137,26 +13148,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -13165,10 +13176,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540603</v>
+        <v>540533</v>
       </c>
       <c r="R114" t="n">
-        <v>6943140</v>
+        <v>6943520</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13219,7 +13230,7 @@
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>bränd gammal rest av tallåga</t>
+          <t>grova gamla branhögstubbar, delvis av skostenstyp</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -13241,7 +13252,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119539945</v>
+        <v>119540009</v>
       </c>
       <c r="B115" t="n">
         <v>78263</v>
@@ -13285,10 +13296,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540496</v>
+        <v>540648</v>
       </c>
       <c r="R115" t="n">
-        <v>6943786</v>
+        <v>6943157</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13339,7 +13350,7 @@
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>mycket grov och hög gammal brandhögstubbe</t>
+          <t>7 m hög, grov gammal tallhögstubbe med brandspår</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -13361,10 +13372,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119539972</v>
+        <v>119539989</v>
       </c>
       <c r="B116" t="n">
-        <v>78263</v>
+        <v>80483</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13377,26 +13388,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -13405,10 +13416,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540533</v>
+        <v>540566</v>
       </c>
       <c r="R116" t="n">
-        <v>6943520</v>
+        <v>6943314</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13454,12 +13465,12 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>grova gamla branhögstubbar, delvis av skostenstyp</t>
+          <t>mycket grov skorstenshögsubbe, ser ut att ha varit boplats för slaguggla</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -13481,10 +13492,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119540017</v>
+        <v>119539992</v>
       </c>
       <c r="B117" t="n">
-        <v>79115</v>
+        <v>78171</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13497,21 +13508,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -13525,10 +13536,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540587</v>
+        <v>540574</v>
       </c>
       <c r="R117" t="n">
-        <v>6943110</v>
+        <v>6943313</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13574,12 +13585,12 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>grov och hård gammal tallhögstubbe</t>
+          <t>gammal, murken tallåga, upphängd mot block</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -13601,10 +13612,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119539964</v>
+        <v>119540022</v>
       </c>
       <c r="B118" t="n">
-        <v>79607</v>
+        <v>90399</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13617,21 +13628,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>6020</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -13645,10 +13656,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540615</v>
+        <v>540595</v>
       </c>
       <c r="R118" t="n">
-        <v>6943357</v>
+        <v>6943080</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13694,12 +13705,12 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog med lövinslag på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>asphögstubbe av senvuxen gammal asp</t>
+          <t>på bark under hängande, ca 10 år gammal asplåga av 130-årig asp, 22 cm bred</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13721,10 +13732,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119539960</v>
+        <v>119539957</v>
       </c>
       <c r="B119" t="n">
-        <v>97907</v>
+        <v>91547</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13733,25 +13744,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>5836</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pers.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13761,10 +13772,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540627</v>
+        <v>540602</v>
       </c>
       <c r="R119" t="n">
-        <v>6943420</v>
+        <v>6943483</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13832,10 +13843,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119540026</v>
+        <v>119539953</v>
       </c>
       <c r="B120" t="n">
-        <v>78171</v>
+        <v>89252</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13844,25 +13855,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -13876,10 +13887,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540609</v>
+        <v>540526</v>
       </c>
       <c r="R120" t="n">
-        <v>6942963</v>
+        <v>6943618</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13925,12 +13936,12 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>grov äldre tallåga</t>
+          <t>sandig fläck</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -13952,10 +13963,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119539992</v>
+        <v>119539979</v>
       </c>
       <c r="B121" t="n">
-        <v>78171</v>
+        <v>90573</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13964,25 +13975,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>353</v>
+        <v>1205</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -13996,10 +14007,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>540574</v>
+        <v>540597</v>
       </c>
       <c r="R121" t="n">
-        <v>6943313</v>
+        <v>6943485</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14045,12 +14056,12 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>gammal, murken tallåga, upphängd mot block</t>
+          <t>grövre asplåga</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14072,10 +14083,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119539985</v>
+        <v>119540023</v>
       </c>
       <c r="B122" t="n">
-        <v>90712</v>
+        <v>79567</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14084,30 +14095,30 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1503</v>
+        <v>229497</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -14116,10 +14127,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>540568</v>
+        <v>540680</v>
       </c>
       <c r="R122" t="n">
-        <v>6943327</v>
+        <v>6942997</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14165,12 +14176,12 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog med lövinslag på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>grov lumpad talltopp från 1800-talet</t>
+          <t>grova gamla aspar</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14192,10 +14203,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119540002</v>
+        <v>119539952</v>
       </c>
       <c r="B123" t="n">
-        <v>91883</v>
+        <v>78171</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14208,21 +14219,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5448</v>
+        <v>353</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -14236,10 +14247,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>540623</v>
+        <v>540543</v>
       </c>
       <c r="R123" t="n">
-        <v>6943285</v>
+        <v>6943622</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14285,12 +14296,12 @@
       </c>
       <c r="AI123" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>sandig mark under gammal murken tallåga</t>
+          <t>fallen brandstubbe</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -14312,10 +14323,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119539954</v>
+        <v>119539976</v>
       </c>
       <c r="B124" t="n">
-        <v>78263</v>
+        <v>79607</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14328,26 +14339,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -14356,10 +14367,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>540579</v>
+        <v>540597</v>
       </c>
       <c r="R124" t="n">
-        <v>6943545</v>
+        <v>6943485</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14405,12 +14416,7 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>grova gammal brandhögstubbe</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14432,10 +14438,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119539950</v>
+        <v>119540010</v>
       </c>
       <c r="B125" t="n">
-        <v>92030</v>
+        <v>90488</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14448,21 +14454,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -14476,10 +14482,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540558</v>
+        <v>540638</v>
       </c>
       <c r="R125" t="n">
-        <v>6943647</v>
+        <v>6943153</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14530,7 +14536,7 @@
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>bränd gammal tallåga</t>
+          <t>gammal klen men hård tallåga, hängande på block</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -14552,10 +14558,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119539943</v>
+        <v>119540027</v>
       </c>
       <c r="B126" t="n">
-        <v>79144</v>
+        <v>91310</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14564,38 +14570,42 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>1958</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(Murrill) Pouzar</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>540529</v>
+        <v>540680</v>
       </c>
       <c r="R126" t="n">
-        <v>6943889</v>
+        <v>6942953</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14646,7 +14656,7 @@
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>grova gamla tallstubbar från dimensionsavverkningen</t>
+          <t>i hålrum under rotben av gammal bränd tallåga</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -14668,10 +14678,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119539940</v>
+        <v>119539975</v>
       </c>
       <c r="B127" t="n">
-        <v>91884</v>
+        <v>87406</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14684,21 +14694,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5449</v>
+        <v>4412</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14708,10 +14718,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>540551</v>
+        <v>540583</v>
       </c>
       <c r="R127" t="n">
-        <v>6943379</v>
+        <v>6943504</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14757,12 +14767,7 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr sandig moränmark</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>sandfläck</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -14784,10 +14789,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119540013</v>
+        <v>119539985</v>
       </c>
       <c r="B128" t="n">
-        <v>89633</v>
+        <v>90712</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14796,25 +14801,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1962</v>
+        <v>1503</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -14828,10 +14833,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>540603</v>
+        <v>540568</v>
       </c>
       <c r="R128" t="n">
-        <v>6943140</v>
+        <v>6943327</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14877,12 +14882,12 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>under bränd gammal rest av tallåga</t>
+          <t>grov lumpad talltopp från 1800-talet</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -14904,10 +14909,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119539996</v>
+        <v>119540015</v>
       </c>
       <c r="B129" t="n">
-        <v>92030</v>
+        <v>79144</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14920,21 +14925,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -14948,10 +14953,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>540597</v>
+        <v>540603</v>
       </c>
       <c r="R129" t="n">
-        <v>6943340</v>
+        <v>6943140</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14997,12 +15002,12 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>gammal rest av tallåga</t>
+          <t>bränd gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -15024,10 +15029,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119539946</v>
+        <v>119540017</v>
       </c>
       <c r="B130" t="n">
-        <v>78171</v>
+        <v>79115</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15040,21 +15045,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -15068,10 +15073,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>540509</v>
+        <v>540587</v>
       </c>
       <c r="R130" t="n">
-        <v>6943761</v>
+        <v>6943110</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15122,7 +15127,7 @@
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>gammal vindfälld tallåga</t>
+          <t>grov och hård gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -15260,10 +15265,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119539959</v>
+        <v>119539988</v>
       </c>
       <c r="B132" t="n">
-        <v>86410</v>
+        <v>78263</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15272,38 +15277,42 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>249228</v>
+        <v>228912</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>540617</v>
+        <v>540570</v>
       </c>
       <c r="R132" t="n">
-        <v>6943447</v>
+        <v>6943318</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15349,12 +15358,12 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>barrmatta under grov gran</t>
+          <t>mycket grov, 4 m hög tallhögsubbe, med kol ända upp</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -15376,7 +15385,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119540006</v>
+        <v>119540024</v>
       </c>
       <c r="B133" t="n">
         <v>90712</v>
@@ -15420,10 +15429,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540638</v>
+        <v>540648</v>
       </c>
       <c r="R133" t="n">
-        <v>6943255</v>
+        <v>6943001</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15474,7 +15483,7 @@
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>rest av gammal bränd tallåga</t>
+          <t>sidan av gammal tallåga med mosshätta</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -15496,10 +15505,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119540020</v>
+        <v>119540006</v>
       </c>
       <c r="B134" t="n">
-        <v>78263</v>
+        <v>90712</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15508,30 +15517,30 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -15540,10 +15549,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>540601</v>
+        <v>540638</v>
       </c>
       <c r="R134" t="n">
-        <v>6943111</v>
+        <v>6943255</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15594,7 +15603,7 @@
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>grova gamla brandstubbar</t>
+          <t>rest av gammal bränd tallåga</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -15616,10 +15625,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119540028</v>
+        <v>119539973</v>
       </c>
       <c r="B135" t="n">
-        <v>78263</v>
+        <v>90058</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15632,38 +15641,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>228912</v>
+        <v>5734</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Druvfingersvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramaria botrytis</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bourdot</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540675</v>
+        <v>540583</v>
       </c>
       <c r="R135" t="n">
-        <v>6942950</v>
+        <v>6943506</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15709,12 +15714,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15736,10 +15736,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119540010</v>
+        <v>119540021</v>
       </c>
       <c r="B136" t="n">
-        <v>90488</v>
+        <v>78171</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15752,21 +15752,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -15780,10 +15780,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540638</v>
+        <v>540594</v>
       </c>
       <c r="R136" t="n">
-        <v>6943153</v>
+        <v>6943086</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15834,7 +15834,7 @@
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>gammal klen men hård tallåga, hängande på block</t>
+          <t>äldre tallåga, vindfälle</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>

--- a/artfynd/A 27954-2021 artfynd.xlsx
+++ b/artfynd/A 27954-2021 artfynd.xlsx
@@ -9922,10 +9922,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119539948</v>
+        <v>119539965</v>
       </c>
       <c r="B87" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9938,26 +9938,26 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9966,10 +9966,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540596</v>
+        <v>540562</v>
       </c>
       <c r="R87" t="n">
-        <v>6943630</v>
+        <v>6943482</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10015,12 +10015,12 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>gamla hårda tallågor</t>
+          <t>sandig fläck</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10162,10 +10162,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119540018</v>
+        <v>119539948</v>
       </c>
       <c r="B89" t="n">
-        <v>78262</v>
+        <v>78171</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10178,26 +10178,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10206,10 +10206,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540587</v>
+        <v>540596</v>
       </c>
       <c r="R89" t="n">
-        <v>6943110</v>
+        <v>6943630</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>grov och hård gammal tallhögstubbe</t>
+          <t>gamla hårda tallågor</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10402,10 +10402,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119539965</v>
+        <v>119540018</v>
       </c>
       <c r="B91" t="n">
-        <v>91856</v>
+        <v>78262</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10418,21 +10418,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2059</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -10446,10 +10446,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540562</v>
+        <v>540587</v>
       </c>
       <c r="R91" t="n">
-        <v>6943482</v>
+        <v>6943110</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10495,12 +10495,12 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>sandig fläck</t>
+          <t>grov och hård gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10522,10 +10522,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119539943</v>
+        <v>119539940</v>
       </c>
       <c r="B92" t="n">
-        <v>79144</v>
+        <v>91884</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10538,21 +10538,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10562,10 +10562,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>540529</v>
+        <v>540551</v>
       </c>
       <c r="R92" t="n">
-        <v>6943889</v>
+        <v>6943379</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10611,12 +10611,12 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr sandig moränmark</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>grova gamla tallstubbar från dimensionsavverkningen</t>
+          <t>sandfläck</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10638,10 +10638,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119539940</v>
+        <v>119539943</v>
       </c>
       <c r="B93" t="n">
-        <v>91884</v>
+        <v>79144</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10654,21 +10654,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10678,10 +10678,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540551</v>
+        <v>540529</v>
       </c>
       <c r="R93" t="n">
-        <v>6943379</v>
+        <v>6943889</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10727,12 +10727,12 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr sandig moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>sandfläck</t>
+          <t>grova gamla tallstubbar från dimensionsavverkningen</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -11701,10 +11701,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119540004</v>
+        <v>119539996</v>
       </c>
       <c r="B102" t="n">
-        <v>91886</v>
+        <v>92030</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11713,25 +11713,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>232140</v>
+        <v>2079</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -11745,10 +11745,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540626</v>
+        <v>540597</v>
       </c>
       <c r="R102" t="n">
-        <v>6943267</v>
+        <v>6943340</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>sandig mark under äldre, klen, självgallrad tallåga</t>
+          <t>gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -11821,10 +11821,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119539996</v>
+        <v>119539970</v>
       </c>
       <c r="B103" t="n">
-        <v>92030</v>
+        <v>78171</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11837,21 +11837,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -11865,10 +11865,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540597</v>
+        <v>540558</v>
       </c>
       <c r="R103" t="n">
-        <v>6943340</v>
+        <v>6943477</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11919,7 +11919,7 @@
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>gammal rest av tallåga</t>
+          <t>grov rest av gammal tallåga med brandspår</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -11941,7 +11941,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119539970</v>
+        <v>119540012</v>
       </c>
       <c r="B104" t="n">
         <v>78171</v>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -11985,10 +11985,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>540558</v>
+        <v>540638</v>
       </c>
       <c r="R104" t="n">
-        <v>6943477</v>
+        <v>6943153</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12034,12 +12034,12 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>grov rest av gammal tallåga med brandspår</t>
+          <t>gamla klena men hårda tallågor, hängande på block</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -12061,10 +12061,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119540012</v>
+        <v>119539960</v>
       </c>
       <c r="B105" t="n">
-        <v>78171</v>
+        <v>97907</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12073,42 +12073,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540638</v>
+        <v>540627</v>
       </c>
       <c r="R105" t="n">
-        <v>6943153</v>
+        <v>6943420</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12154,12 +12150,7 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>gamla klena men hårda tallågor, hängande på block</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12181,10 +12172,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119540002</v>
+        <v>119540004</v>
       </c>
       <c r="B106" t="n">
-        <v>91883</v>
+        <v>91886</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12193,25 +12184,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5448</v>
+        <v>232140</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -12225,10 +12216,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540623</v>
+        <v>540626</v>
       </c>
       <c r="R106" t="n">
-        <v>6943285</v>
+        <v>6943267</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12279,7 +12270,7 @@
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>sandig mark under gammal murken tallåga</t>
+          <t>sandig mark under äldre, klen, självgallrad tallåga</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12421,10 +12412,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119539960</v>
+        <v>119540002</v>
       </c>
       <c r="B108" t="n">
-        <v>97907</v>
+        <v>91883</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12433,38 +12424,42 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>540627</v>
+        <v>540623</v>
       </c>
       <c r="R108" t="n">
-        <v>6943420</v>
+        <v>6943285</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12510,7 +12505,12 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>sandig mark under gammal murken tallåga</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12652,10 +12652,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119539954</v>
+        <v>119539967</v>
       </c>
       <c r="B110" t="n">
-        <v>78263</v>
+        <v>89964</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12664,25 +12664,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>5685</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -12696,10 +12696,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>540579</v>
+        <v>540570</v>
       </c>
       <c r="R110" t="n">
-        <v>6943545</v>
+        <v>6943440</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12745,12 +12745,12 @@
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>grova gammal brandhögstubbe</t>
+          <t>äldre murket tallvindfälle</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12772,10 +12772,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119539967</v>
+        <v>119539954</v>
       </c>
       <c r="B111" t="n">
-        <v>89964</v>
+        <v>78263</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12784,25 +12784,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5685</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -12816,10 +12816,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>540570</v>
+        <v>540579</v>
       </c>
       <c r="R111" t="n">
-        <v>6943440</v>
+        <v>6943545</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12865,12 +12865,12 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>äldre murket tallvindfälle</t>
+          <t>grova gammal brandhögstubbe</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -13132,10 +13132,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119539972</v>
+        <v>119539989</v>
       </c>
       <c r="B114" t="n">
-        <v>78263</v>
+        <v>80483</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13148,26 +13148,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>1049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -13176,10 +13176,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540533</v>
+        <v>540566</v>
       </c>
       <c r="R114" t="n">
-        <v>6943520</v>
+        <v>6943314</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13225,12 +13225,12 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>grova gamla branhögstubbar, delvis av skostenstyp</t>
+          <t>mycket grov skorstenshögsubbe, ser ut att ha varit boplats för slaguggla</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -13252,10 +13252,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119540009</v>
+        <v>119539992</v>
       </c>
       <c r="B115" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13268,21 +13268,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -13296,10 +13296,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540648</v>
+        <v>540574</v>
       </c>
       <c r="R115" t="n">
-        <v>6943157</v>
+        <v>6943313</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13345,12 +13345,12 @@
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>7 m hög, grov gammal tallhögstubbe med brandspår</t>
+          <t>gammal, murken tallåga, upphängd mot block</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -13372,10 +13372,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119539989</v>
+        <v>119540022</v>
       </c>
       <c r="B116" t="n">
-        <v>80483</v>
+        <v>90399</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13388,21 +13388,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1049</v>
+        <v>6020</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -13416,10 +13416,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>540566</v>
+        <v>540595</v>
       </c>
       <c r="R116" t="n">
-        <v>6943314</v>
+        <v>6943080</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13465,12 +13465,12 @@
       </c>
       <c r="AI116" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog med lövinslag på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>mycket grov skorstenshögsubbe, ser ut att ha varit boplats för slaguggla</t>
+          <t>på bark under hängande, ca 10 år gammal asplåga av 130-årig asp, 22 cm bred</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr"/>
@@ -13492,10 +13492,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119539992</v>
+        <v>119539972</v>
       </c>
       <c r="B117" t="n">
-        <v>78171</v>
+        <v>78263</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13508,26 +13508,26 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13536,10 +13536,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540574</v>
+        <v>540533</v>
       </c>
       <c r="R117" t="n">
-        <v>6943313</v>
+        <v>6943520</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13585,12 +13585,12 @@
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>gammal, murken tallåga, upphängd mot block</t>
+          <t>grova gamla branhögstubbar, delvis av skostenstyp</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -13612,10 +13612,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119540022</v>
+        <v>119540009</v>
       </c>
       <c r="B118" t="n">
-        <v>90399</v>
+        <v>78263</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13628,21 +13628,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6020</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Oljetagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Sistotrema raduloides</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Donk</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -13656,10 +13656,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540595</v>
+        <v>540648</v>
       </c>
       <c r="R118" t="n">
-        <v>6943080</v>
+        <v>6943157</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog med lövinslag på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>på bark under hängande, ca 10 år gammal asplåga av 130-årig asp, 22 cm bred</t>
+          <t>7 m hög, grov gammal tallhögstubbe med brandspår</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -14203,10 +14203,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119539952</v>
+        <v>119540010</v>
       </c>
       <c r="B123" t="n">
-        <v>78171</v>
+        <v>90488</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14219,21 +14219,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -14247,10 +14247,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>540543</v>
+        <v>540638</v>
       </c>
       <c r="R123" t="n">
-        <v>6943622</v>
+        <v>6943153</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>fallen brandstubbe</t>
+          <t>gammal klen men hård tallåga, hängande på block</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -14323,10 +14323,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119539976</v>
+        <v>119539952</v>
       </c>
       <c r="B124" t="n">
-        <v>79607</v>
+        <v>78171</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14339,26 +14339,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P124" t="inlineStr">
@@ -14367,10 +14367,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>540597</v>
+        <v>540543</v>
       </c>
       <c r="R124" t="n">
-        <v>6943485</v>
+        <v>6943622</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14416,7 +14416,12 @@
       </c>
       <c r="AI124" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>fallen brandstubbe</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14438,10 +14443,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119540010</v>
+        <v>119539976</v>
       </c>
       <c r="B125" t="n">
-        <v>90488</v>
+        <v>79607</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14454,26 +14459,26 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>3242</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -14482,10 +14487,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540638</v>
+        <v>540597</v>
       </c>
       <c r="R125" t="n">
-        <v>6943153</v>
+        <v>6943485</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14531,12 +14536,7 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>gammal klen men hård tallåga, hängande på block</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -15149,10 +15149,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119539939</v>
+        <v>119539988</v>
       </c>
       <c r="B131" t="n">
-        <v>90067</v>
+        <v>78263</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15161,38 +15161,42 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>256703</v>
+        <v>228912</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>540599</v>
+        <v>540570</v>
       </c>
       <c r="R131" t="n">
-        <v>6943128</v>
+        <v>6943318</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15238,12 +15242,12 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr sandig moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>sandfläck</t>
+          <t>mycket grov, 4 m hög tallhögsubbe, med kol ända upp</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -15265,10 +15269,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119539988</v>
+        <v>119539939</v>
       </c>
       <c r="B132" t="n">
-        <v>78263</v>
+        <v>90067</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15277,42 +15281,38 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228912</v>
+        <v>256703</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>540570</v>
+        <v>540599</v>
       </c>
       <c r="R132" t="n">
-        <v>6943318</v>
+        <v>6943128</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15358,12 +15358,12 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr sandig moränmark</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>mycket grov, 4 m hög tallhögsubbe, med kol ända upp</t>
+          <t>sandfläck</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -15625,10 +15625,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119539973</v>
+        <v>119540021</v>
       </c>
       <c r="B135" t="n">
-        <v>90058</v>
+        <v>78171</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15641,34 +15641,38 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5734</v>
+        <v>353</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Druvfingersvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramaria botrytis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bourdot</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540583</v>
+        <v>540594</v>
       </c>
       <c r="R135" t="n">
-        <v>6943506</v>
+        <v>6943086</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15714,7 +15718,12 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>äldre tallåga, vindfälle</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15736,10 +15745,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119540021</v>
+        <v>119539973</v>
       </c>
       <c r="B136" t="n">
-        <v>78171</v>
+        <v>90058</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15752,38 +15761,34 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>353</v>
+        <v>5734</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Druvfingersvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramaria botrytis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bourdot</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540594</v>
+        <v>540583</v>
       </c>
       <c r="R136" t="n">
-        <v>6943086</v>
+        <v>6943506</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15829,12 +15834,7 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>äldre tallåga, vindfälle</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>

--- a/artfynd/A 27954-2021 artfynd.xlsx
+++ b/artfynd/A 27954-2021 artfynd.xlsx
@@ -9322,10 +9322,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119540028</v>
+        <v>119539957</v>
       </c>
       <c r="B82" t="n">
-        <v>78263</v>
+        <v>91547</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9334,42 +9334,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>5836</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>540675</v>
+        <v>540602</v>
       </c>
       <c r="R82" t="n">
-        <v>6942950</v>
+        <v>6943483</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9415,12 +9411,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9442,10 +9433,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119539955</v>
+        <v>119539960</v>
       </c>
       <c r="B83" t="n">
-        <v>91834</v>
+        <v>97907</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9454,42 +9445,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>540583</v>
+        <v>540627</v>
       </c>
       <c r="R83" t="n">
-        <v>6943542</v>
+        <v>6943420</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9536,11 +9523,6 @@
       <c r="AI83" t="inlineStr">
         <is>
           <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>i hålrum under rotben av gammal bränd tallåga</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9562,10 +9544,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119539999</v>
+        <v>119539954</v>
       </c>
       <c r="B84" t="n">
-        <v>90576</v>
+        <v>78263</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9578,21 +9560,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1204</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -9606,10 +9588,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>540637</v>
+        <v>540579</v>
       </c>
       <c r="R84" t="n">
-        <v>6943297</v>
+        <v>6943545</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9655,12 +9637,12 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>grov gammal tallåga</t>
+          <t>grova gammal brandhögstubbe</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9682,10 +9664,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119540025</v>
+        <v>119539944</v>
       </c>
       <c r="B85" t="n">
-        <v>80483</v>
+        <v>79115</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9698,21 +9680,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1049</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9726,10 +9708,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>540645</v>
+        <v>540529</v>
       </c>
       <c r="R85" t="n">
-        <v>6942999</v>
+        <v>6943889</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9780,7 +9762,7 @@
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>grov gammal skorstenshögstubbe</t>
+          <t>grov gammal tallstubbe från dimensionsavverkningen</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9802,10 +9784,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119539964</v>
+        <v>119540012</v>
       </c>
       <c r="B86" t="n">
-        <v>79607</v>
+        <v>78171</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9818,26 +9800,26 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9846,10 +9828,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>540615</v>
+        <v>540638</v>
       </c>
       <c r="R86" t="n">
-        <v>6943357</v>
+        <v>6943153</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9895,12 +9877,12 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>asphögstubbe av senvuxen gammal asp</t>
+          <t>gamla klena men hårda tallågor, hängande på block</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -9922,10 +9904,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119539965</v>
+        <v>119540023</v>
       </c>
       <c r="B87" t="n">
-        <v>91856</v>
+        <v>79567</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9934,30 +9916,30 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2059</v>
+        <v>229497</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9966,10 +9948,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>540562</v>
+        <v>540680</v>
       </c>
       <c r="R87" t="n">
-        <v>6943482</v>
+        <v>6942997</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10015,12 +9997,12 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog med lövinslag på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>sandig fläck</t>
+          <t>grova gamla aspar</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10042,10 +10024,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119539946</v>
+        <v>119539949</v>
       </c>
       <c r="B88" t="n">
-        <v>78171</v>
+        <v>91856</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10058,21 +10040,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -10086,10 +10068,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>540509</v>
+        <v>540590</v>
       </c>
       <c r="R88" t="n">
-        <v>6943761</v>
+        <v>6943641</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10140,7 +10122,7 @@
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>gammal vindfälld tallåga</t>
+          <t>sandig mark</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10162,10 +10144,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119539948</v>
+        <v>119540010</v>
       </c>
       <c r="B89" t="n">
-        <v>78171</v>
+        <v>90488</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10178,26 +10160,26 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10206,10 +10188,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>540596</v>
+        <v>540638</v>
       </c>
       <c r="R89" t="n">
-        <v>6943630</v>
+        <v>6943153</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10260,7 +10242,7 @@
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>gamla hårda tallågor</t>
+          <t>gammal klen men hård tallåga, hängande på block</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10282,10 +10264,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119540013</v>
+        <v>119540027</v>
       </c>
       <c r="B90" t="n">
-        <v>89633</v>
+        <v>91310</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10294,25 +10276,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1962</v>
+        <v>1958</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -10326,10 +10308,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>540603</v>
+        <v>540680</v>
       </c>
       <c r="R90" t="n">
-        <v>6943140</v>
+        <v>6942953</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10380,7 +10362,7 @@
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>under bränd gammal rest av tallåga</t>
+          <t>i hålrum under rotben av gammal bränd tallåga</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10402,10 +10384,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119540018</v>
+        <v>119539959</v>
       </c>
       <c r="B91" t="n">
-        <v>78262</v>
+        <v>86410</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10414,42 +10396,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>249228</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>540587</v>
+        <v>540617</v>
       </c>
       <c r="R91" t="n">
-        <v>6943110</v>
+        <v>6943447</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10495,12 +10473,12 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>grov och hård gammal tallhögstubbe</t>
+          <t>barrmatta under grov gran</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10522,10 +10500,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119539940</v>
+        <v>119540020</v>
       </c>
       <c r="B92" t="n">
-        <v>91884</v>
+        <v>78263</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10538,34 +10516,38 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>540551</v>
+        <v>540601</v>
       </c>
       <c r="R92" t="n">
-        <v>6943379</v>
+        <v>6943111</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10611,12 +10593,12 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr sandig moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>sandfläck</t>
+          <t>grova gamla brandstubbar</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10638,10 +10620,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119539943</v>
+        <v>119539999</v>
       </c>
       <c r="B93" t="n">
-        <v>79144</v>
+        <v>90576</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10654,34 +10636,38 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>540529</v>
+        <v>540637</v>
       </c>
       <c r="R93" t="n">
-        <v>6943889</v>
+        <v>6943297</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10727,12 +10713,12 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>grova gamla tallstubbar från dimensionsavverkningen</t>
+          <t>grov gammal tallåga</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
@@ -10754,7 +10740,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119539949</v>
+        <v>119539965</v>
       </c>
       <c r="B94" t="n">
         <v>91856</v>
@@ -10798,10 +10784,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>540590</v>
+        <v>540562</v>
       </c>
       <c r="R94" t="n">
-        <v>6943641</v>
+        <v>6943482</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10847,12 +10833,12 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>sandig mark</t>
+          <t>sandig fläck</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -10874,10 +10860,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119540026</v>
+        <v>119539975</v>
       </c>
       <c r="B95" t="n">
-        <v>78171</v>
+        <v>87406</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10890,38 +10876,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>4412</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>540609</v>
+        <v>540583</v>
       </c>
       <c r="R95" t="n">
-        <v>6942963</v>
+        <v>6943504</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10967,12 +10949,7 @@
       </c>
       <c r="AI95" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>grov äldre tallåga</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
         </is>
       </c>
       <c r="AT95" t="inlineStr"/>
@@ -10994,7 +10971,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119539941</v>
+        <v>119539940</v>
       </c>
       <c r="B96" t="n">
         <v>91884</v>
@@ -11034,10 +11011,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>540526</v>
+        <v>540551</v>
       </c>
       <c r="R96" t="n">
-        <v>6943625</v>
+        <v>6943379</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11084,6 +11061,11 @@
       <c r="AI96" t="inlineStr">
         <is>
           <t>140-årig tallnaturskog på blockig torr sandig moränmark</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>sandfläck</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
@@ -11105,10 +11087,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119539959</v>
+        <v>119539988</v>
       </c>
       <c r="B97" t="n">
-        <v>86410</v>
+        <v>78263</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11117,38 +11099,42 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>249228</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Frøslev, T.S.Jeppesen &amp; Brandrud</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>540617</v>
+        <v>540570</v>
       </c>
       <c r="R97" t="n">
-        <v>6943447</v>
+        <v>6943318</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11194,12 +11180,12 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>barrmatta under grov gran</t>
+          <t>mycket grov, 4 m hög tallhögsubbe, med kol ända upp</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11221,10 +11207,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119539950</v>
+        <v>119540018</v>
       </c>
       <c r="B98" t="n">
-        <v>92030</v>
+        <v>78262</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11237,21 +11223,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2079</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -11265,10 +11251,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>540558</v>
+        <v>540587</v>
       </c>
       <c r="R98" t="n">
-        <v>6943647</v>
+        <v>6943110</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11319,7 +11305,7 @@
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>bränd gammal tallåga</t>
+          <t>grov och hård gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11341,10 +11327,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119539962</v>
+        <v>119539948</v>
       </c>
       <c r="B99" t="n">
-        <v>90712</v>
+        <v>78171</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11353,30 +11339,30 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11385,10 +11371,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>540625</v>
+        <v>540596</v>
       </c>
       <c r="R99" t="n">
-        <v>6943399</v>
+        <v>6943630</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11434,12 +11420,12 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>140-årig, lövrik tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>grov rest av gammal tallåga med brandspår</t>
+          <t>gamla hårda tallågor</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11461,10 +11447,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119539947</v>
+        <v>119539952</v>
       </c>
       <c r="B100" t="n">
-        <v>91884</v>
+        <v>78171</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11477,21 +11463,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5449</v>
+        <v>353</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -11505,10 +11491,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>540559</v>
+        <v>540543</v>
       </c>
       <c r="R100" t="n">
-        <v>6943714</v>
+        <v>6943622</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11559,7 +11545,7 @@
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>sandig mark</t>
+          <t>fallen brandstubbe</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -11581,7 +11567,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119540020</v>
+        <v>119539945</v>
       </c>
       <c r="B101" t="n">
         <v>78263</v>
@@ -11616,7 +11602,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -11625,10 +11611,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>540601</v>
+        <v>540496</v>
       </c>
       <c r="R101" t="n">
-        <v>6943111</v>
+        <v>6943786</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11679,7 +11665,7 @@
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>grova gamla brandstubbar</t>
+          <t>mycket grov och hög gammal brandhögstubbe</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -11701,10 +11687,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119539996</v>
+        <v>119539967</v>
       </c>
       <c r="B102" t="n">
-        <v>92030</v>
+        <v>89964</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11713,25 +11699,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2079</v>
+        <v>5685</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -11745,10 +11731,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>540597</v>
+        <v>540570</v>
       </c>
       <c r="R102" t="n">
-        <v>6943340</v>
+        <v>6943440</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11799,7 +11785,7 @@
       </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>gammal rest av tallåga</t>
+          <t>äldre murket tallvindfälle</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -11821,10 +11807,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119539970</v>
+        <v>119539973</v>
       </c>
       <c r="B103" t="n">
-        <v>78171</v>
+        <v>90058</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11837,38 +11823,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>353</v>
+        <v>5734</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Druvfingersvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramaria botrytis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bourdot</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>540558</v>
+        <v>540583</v>
       </c>
       <c r="R103" t="n">
-        <v>6943477</v>
+        <v>6943506</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11914,12 +11896,7 @@
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>grov rest av gammal tallåga med brandspår</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -11941,10 +11918,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119540012</v>
+        <v>119539941</v>
       </c>
       <c r="B104" t="n">
-        <v>78171</v>
+        <v>91884</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11957,38 +11934,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>353</v>
+        <v>5449</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>540638</v>
+        <v>540526</v>
       </c>
       <c r="R104" t="n">
-        <v>6943153</v>
+        <v>6943625</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12034,12 +12007,7 @@
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>gamla klena men hårda tallågor, hängande på block</t>
+          <t>140-årig tallnaturskog på blockig torr sandig moränmark</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr"/>
@@ -12061,10 +12029,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119539960</v>
+        <v>119539972</v>
       </c>
       <c r="B105" t="n">
-        <v>97907</v>
+        <v>78263</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12073,38 +12041,42 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>540627</v>
+        <v>540533</v>
       </c>
       <c r="R105" t="n">
-        <v>6943420</v>
+        <v>6943520</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12150,7 +12122,12 @@
       </c>
       <c r="AI105" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>grova gamla branhögstubbar, delvis av skostenstyp</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12172,10 +12149,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119540004</v>
+        <v>119539970</v>
       </c>
       <c r="B106" t="n">
-        <v>91886</v>
+        <v>78171</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12184,25 +12161,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>232140</v>
+        <v>353</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -12216,10 +12193,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>540626</v>
+        <v>540558</v>
       </c>
       <c r="R106" t="n">
-        <v>6943267</v>
+        <v>6943477</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12270,7 +12247,7 @@
       </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>sandig mark under äldre, klen, självgallrad tallåga</t>
+          <t>grov rest av gammal tallåga med brandspår</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12292,10 +12269,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119539994</v>
+        <v>119539989</v>
       </c>
       <c r="B107" t="n">
-        <v>90712</v>
+        <v>80483</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12304,25 +12281,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1503</v>
+        <v>1049</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -12336,10 +12313,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>540593</v>
+        <v>540566</v>
       </c>
       <c r="R107" t="n">
-        <v>6943335</v>
+        <v>6943314</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12390,7 +12367,7 @@
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>gammal, grov tallåga, upphängd mot block</t>
+          <t>mycket grov skorstenshögsubbe, ser ut att ha varit boplats för slaguggla</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12412,10 +12389,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119540002</v>
+        <v>119539979</v>
       </c>
       <c r="B108" t="n">
-        <v>91883</v>
+        <v>90573</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12424,25 +12401,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5448</v>
+        <v>1205</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -12456,10 +12433,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>540623</v>
+        <v>540597</v>
       </c>
       <c r="R108" t="n">
-        <v>6943285</v>
+        <v>6943485</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12505,12 +12482,12 @@
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>sandig mark under gammal murken tallåga</t>
+          <t>grövre asplåga</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12532,10 +12509,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119539945</v>
+        <v>119540024</v>
       </c>
       <c r="B109" t="n">
-        <v>78263</v>
+        <v>90712</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12544,25 +12521,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -12576,10 +12553,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>540496</v>
+        <v>540648</v>
       </c>
       <c r="R109" t="n">
-        <v>6943786</v>
+        <v>6943001</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12630,7 +12607,7 @@
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>mycket grov och hög gammal brandhögstubbe</t>
+          <t>sidan av gammal tallåga med mosshätta</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12652,10 +12629,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119539967</v>
+        <v>119539994</v>
       </c>
       <c r="B110" t="n">
-        <v>89964</v>
+        <v>90712</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12664,25 +12641,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5685</v>
+        <v>1503</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -12696,10 +12673,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>540570</v>
+        <v>540593</v>
       </c>
       <c r="R110" t="n">
-        <v>6943440</v>
+        <v>6943335</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12750,7 +12727,7 @@
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>äldre murket tallvindfälle</t>
+          <t>gammal, grov tallåga, upphängd mot block</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr"/>
@@ -12772,10 +12749,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119539954</v>
+        <v>119539964</v>
       </c>
       <c r="B111" t="n">
-        <v>78263</v>
+        <v>79607</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12788,21 +12765,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -12816,10 +12793,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>540579</v>
+        <v>540615</v>
       </c>
       <c r="R111" t="n">
-        <v>6943545</v>
+        <v>6943357</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12865,12 +12842,12 @@
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>grova gammal brandhögstubbe</t>
+          <t>asphögstubbe av senvuxen gammal asp</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr"/>
@@ -12892,10 +12869,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119539944</v>
+        <v>119539943</v>
       </c>
       <c r="B112" t="n">
-        <v>79115</v>
+        <v>79144</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12908,28 +12885,24 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
@@ -12990,7 +12963,7 @@
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>grov gammal tallstubbe från dimensionsavverkningen</t>
+          <t>grova gamla tallstubbar från dimensionsavverkningen</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -13012,10 +12985,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119540007</v>
+        <v>119539976</v>
       </c>
       <c r="B113" t="n">
-        <v>78171</v>
+        <v>79607</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13028,21 +13001,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -13056,10 +13029,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>540649</v>
+        <v>540597</v>
       </c>
       <c r="R113" t="n">
-        <v>6943183</v>
+        <v>6943485</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13105,12 +13078,7 @@
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>gamla klena men hårda tallågor, hängande på block</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr"/>
@@ -13132,10 +13100,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119539989</v>
+        <v>119539939</v>
       </c>
       <c r="B114" t="n">
-        <v>80483</v>
+        <v>90067</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13144,42 +13112,38 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1049</v>
+        <v>256703</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>540566</v>
+        <v>540599</v>
       </c>
       <c r="R114" t="n">
-        <v>6943314</v>
+        <v>6943128</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13225,12 +13189,12 @@
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr sandig moränmark</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>mycket grov skorstenshögsubbe, ser ut att ha varit boplats för slaguggla</t>
+          <t>sandfläck</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr"/>
@@ -13252,10 +13216,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119539992</v>
+        <v>119540002</v>
       </c>
       <c r="B115" t="n">
-        <v>78171</v>
+        <v>91883</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13268,21 +13232,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>353</v>
+        <v>5448</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -13296,10 +13260,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>540574</v>
+        <v>540623</v>
       </c>
       <c r="R115" t="n">
-        <v>6943313</v>
+        <v>6943285</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13350,7 +13314,7 @@
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>gammal, murken tallåga, upphängd mot block</t>
+          <t>sandig mark under gammal murken tallåga</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -13492,10 +13456,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119539972</v>
+        <v>119540021</v>
       </c>
       <c r="B117" t="n">
-        <v>78263</v>
+        <v>78171</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -13508,26 +13472,26 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P117" t="inlineStr">
@@ -13536,10 +13500,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>540533</v>
+        <v>540594</v>
       </c>
       <c r="R117" t="n">
-        <v>6943520</v>
+        <v>6943086</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13590,7 +13554,7 @@
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>grova gamla branhögstubbar, delvis av skostenstyp</t>
+          <t>äldre tallåga, vindfälle</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -13612,10 +13576,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119540009</v>
+        <v>119539985</v>
       </c>
       <c r="B118" t="n">
-        <v>78263</v>
+        <v>90712</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13624,25 +13588,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -13656,10 +13620,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>540648</v>
+        <v>540568</v>
       </c>
       <c r="R118" t="n">
-        <v>6943157</v>
+        <v>6943327</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13705,12 +13669,12 @@
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>7 m hög, grov gammal tallhögstubbe med brandspår</t>
+          <t>grov lumpad talltopp från 1800-talet</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr"/>
@@ -13732,10 +13696,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119539957</v>
+        <v>119539996</v>
       </c>
       <c r="B119" t="n">
-        <v>91547</v>
+        <v>92030</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13744,38 +13708,42 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5836</v>
+        <v>2079</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>540602</v>
+        <v>540597</v>
       </c>
       <c r="R119" t="n">
-        <v>6943483</v>
+        <v>6943340</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13821,7 +13789,12 @@
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -13843,10 +13816,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119539953</v>
+        <v>119540017</v>
       </c>
       <c r="B120" t="n">
-        <v>89252</v>
+        <v>79115</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13855,25 +13828,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6276</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -13887,10 +13860,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>540526</v>
+        <v>540587</v>
       </c>
       <c r="R120" t="n">
-        <v>6943618</v>
+        <v>6943110</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13936,12 +13909,12 @@
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>sandig fläck</t>
+          <t>grov och hård gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -13963,10 +13936,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119539979</v>
+        <v>119540025</v>
       </c>
       <c r="B121" t="n">
-        <v>90573</v>
+        <v>80483</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13975,25 +13948,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1205</v>
+        <v>1049</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -14007,10 +13980,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>540597</v>
+        <v>540645</v>
       </c>
       <c r="R121" t="n">
-        <v>6943485</v>
+        <v>6942999</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14056,12 +14029,12 @@
       </c>
       <c r="AI121" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>grövre asplåga</t>
+          <t>grov gammal skorstenshögstubbe</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
@@ -14083,10 +14056,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119540023</v>
+        <v>119540026</v>
       </c>
       <c r="B122" t="n">
-        <v>79567</v>
+        <v>78171</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14095,30 +14068,30 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229497</v>
+        <v>353</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
@@ -14127,10 +14100,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>540680</v>
+        <v>540609</v>
       </c>
       <c r="R122" t="n">
-        <v>6942997</v>
+        <v>6942963</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14176,12 +14149,12 @@
       </c>
       <c r="AI122" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog med lövinslag på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>grova gamla aspar</t>
+          <t>grov äldre tallåga</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14203,10 +14176,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119540010</v>
+        <v>119540007</v>
       </c>
       <c r="B123" t="n">
-        <v>90488</v>
+        <v>78171</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14219,26 +14192,26 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -14247,10 +14220,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>540638</v>
+        <v>540649</v>
       </c>
       <c r="R123" t="n">
-        <v>6943153</v>
+        <v>6943183</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14301,7 +14274,7 @@
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>gammal klen men hård tallåga, hängande på block</t>
+          <t>gamla klena men hårda tallågor, hängande på block</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -14323,7 +14296,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119539952</v>
+        <v>119539946</v>
       </c>
       <c r="B124" t="n">
         <v>78171</v>
@@ -14367,10 +14340,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>540543</v>
+        <v>540509</v>
       </c>
       <c r="R124" t="n">
-        <v>6943622</v>
+        <v>6943761</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14421,7 +14394,7 @@
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>fallen brandstubbe</t>
+          <t>gammal vindfälld tallåga</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14443,10 +14416,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119539976</v>
+        <v>119539947</v>
       </c>
       <c r="B125" t="n">
-        <v>79607</v>
+        <v>91884</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14459,26 +14432,26 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>5449</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
@@ -14487,10 +14460,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>540597</v>
+        <v>540559</v>
       </c>
       <c r="R125" t="n">
-        <v>6943485</v>
+        <v>6943714</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14536,7 +14509,12 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>sandig mark</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -14558,10 +14536,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119540027</v>
+        <v>119539950</v>
       </c>
       <c r="B126" t="n">
-        <v>91310</v>
+        <v>92030</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -14570,25 +14548,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1958</v>
+        <v>2079</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -14602,10 +14580,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>540680</v>
+        <v>540558</v>
       </c>
       <c r="R126" t="n">
-        <v>6942953</v>
+        <v>6943647</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14656,7 +14634,7 @@
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>i hålrum under rotben av gammal bränd tallåga</t>
+          <t>bränd gammal tallåga</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -14678,10 +14656,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119539975</v>
+        <v>119540006</v>
       </c>
       <c r="B127" t="n">
-        <v>87406</v>
+        <v>90712</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -14690,38 +14668,42 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4412</v>
+        <v>1503</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P127" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>540583</v>
+        <v>540638</v>
       </c>
       <c r="R127" t="n">
-        <v>6943504</v>
+        <v>6943255</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14767,7 +14749,12 @@
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>rest av gammal bränd tallåga</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -14789,10 +14776,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119539985</v>
+        <v>119540013</v>
       </c>
       <c r="B128" t="n">
-        <v>90712</v>
+        <v>89633</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -14801,25 +14788,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1503</v>
+        <v>1962</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -14833,10 +14820,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>540568</v>
+        <v>540603</v>
       </c>
       <c r="R128" t="n">
-        <v>6943327</v>
+        <v>6943140</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14882,12 +14869,12 @@
       </c>
       <c r="AI128" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>grov lumpad talltopp från 1800-talet</t>
+          <t>under bränd gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -14909,10 +14896,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119540015</v>
+        <v>119539992</v>
       </c>
       <c r="B129" t="n">
-        <v>79144</v>
+        <v>78171</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -14925,21 +14912,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -14953,10 +14940,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>540603</v>
+        <v>540574</v>
       </c>
       <c r="R129" t="n">
-        <v>6943140</v>
+        <v>6943313</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15002,12 +14989,12 @@
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>bränd gammal rest av tallåga</t>
+          <t>gammal, murken tallåga, upphängd mot block</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -15029,10 +15016,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119540017</v>
+        <v>119539962</v>
       </c>
       <c r="B130" t="n">
-        <v>79115</v>
+        <v>90712</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15041,25 +15028,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -15073,10 +15060,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>540587</v>
+        <v>540625</v>
       </c>
       <c r="R130" t="n">
-        <v>6943110</v>
+        <v>6943399</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15122,12 +15109,12 @@
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig, lövrik tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>grov och hård gammal tallhögstubbe</t>
+          <t>grov rest av gammal tallåga med brandspår</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -15149,7 +15136,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119539988</v>
+        <v>119540009</v>
       </c>
       <c r="B131" t="n">
         <v>78263</v>
@@ -15193,10 +15180,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>540570</v>
+        <v>540648</v>
       </c>
       <c r="R131" t="n">
-        <v>6943318</v>
+        <v>6943157</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15242,12 +15229,12 @@
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr moränmark</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>mycket grov, 4 m hög tallhögsubbe, med kol ända upp</t>
+          <t>7 m hög, grov gammal tallhögstubbe med brandspår</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -15269,10 +15256,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119539939</v>
+        <v>119540004</v>
       </c>
       <c r="B132" t="n">
-        <v>90067</v>
+        <v>91886</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15281,38 +15268,42 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>256703</v>
+        <v>232140</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>540599</v>
+        <v>540626</v>
       </c>
       <c r="R132" t="n">
-        <v>6943128</v>
+        <v>6943267</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15358,12 +15349,12 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig torr sandig moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>sandfläck</t>
+          <t>sandig mark under äldre, klen, självgallrad tallåga</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
@@ -15385,10 +15376,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119540024</v>
+        <v>119540015</v>
       </c>
       <c r="B133" t="n">
-        <v>90712</v>
+        <v>79144</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15397,25 +15388,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -15429,10 +15420,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>540648</v>
+        <v>540603</v>
       </c>
       <c r="R133" t="n">
-        <v>6943001</v>
+        <v>6943140</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15483,7 +15474,7 @@
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>sidan av gammal tallåga med mosshätta</t>
+          <t>bränd gammal rest av tallåga</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
@@ -15505,10 +15496,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119540006</v>
+        <v>119539955</v>
       </c>
       <c r="B134" t="n">
-        <v>90712</v>
+        <v>91834</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -15517,25 +15508,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1503</v>
+        <v>4362</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -15549,10 +15540,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>540638</v>
+        <v>540583</v>
       </c>
       <c r="R134" t="n">
-        <v>6943255</v>
+        <v>6943542</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15598,12 +15589,12 @@
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med blockighet</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>rest av gammal bränd tallåga</t>
+          <t>i hålrum under rotben av gammal bränd tallåga</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr"/>
@@ -15625,10 +15616,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119540021</v>
+        <v>119539953</v>
       </c>
       <c r="B135" t="n">
-        <v>78171</v>
+        <v>89252</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -15637,25 +15628,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>353</v>
+        <v>6276</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -15669,10 +15660,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>540594</v>
+        <v>540526</v>
       </c>
       <c r="R135" t="n">
-        <v>6943086</v>
+        <v>6943618</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15718,12 +15709,12 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+          <t>140-årig tallnaturskog på blockig torr moränmark</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>äldre tallåga, vindfälle</t>
+          <t>sandig fläck</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -15745,10 +15736,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119539973</v>
+        <v>119540028</v>
       </c>
       <c r="B136" t="n">
-        <v>90058</v>
+        <v>78263</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -15761,34 +15752,38 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>5734</v>
+        <v>228912</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Druvfingersvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ramaria botrytis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bourdot</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
           <t>Mellan Övertjärnen och Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>540583</v>
+        <v>540675</v>
       </c>
       <c r="R136" t="n">
-        <v>6943506</v>
+        <v>6942950</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15834,7 +15829,12 @@
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>140-årig lövrik blandnaturskog i rikare terrängsvacka med lågört och blockighet</t>
+          <t>140-årig tallnaturskog på blockig frisk moränmark</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr"/>

--- a/artfynd/A 27954-2021 artfynd.xlsx
+++ b/artfynd/A 27954-2021 artfynd.xlsx
@@ -5527,7 +5527,7 @@
         <v>119231117</v>
       </c>
       <c r="B45" t="n">
-        <v>90183</v>
+        <v>90193</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 27954-2021 artfynd.xlsx
+++ b/artfynd/A 27954-2021 artfynd.xlsx
@@ -5527,7 +5527,7 @@
         <v>119231117</v>
       </c>
       <c r="B45" t="n">
-        <v>90193</v>
+        <v>90205</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>

--- a/artfynd/A 27954-2021 artfynd.xlsx
+++ b/artfynd/A 27954-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119179457</v>
       </c>
       <c r="B2" t="n">
-        <v>57308</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -716,7 +716,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mellantjärnsbodarna (Mellantjärnsbodarna), Mpd</t>
+          <t>Mellantjärnsbodarna, Mellantjärnsbodarna, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">

--- a/artfynd/A 27954-2021 artfynd.xlsx
+++ b/artfynd/A 27954-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119179457</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 27954-2021 artfynd.xlsx
+++ b/artfynd/A 27954-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119179457</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
